--- a/reports/tickets/Sprint26-18/VCST-5378/vcst-5378-test-cases.xlsx
+++ b/reports/tickets/Sprint26-18/VCST-5378/vcst-5378-test-cases.xlsx
@@ -572,17 +572,29 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Find the Epson WorkForce WF-3640 on B2B-store and add one to my cart. Don't use my account, don't check out.</t>
+          <t xml:space="preserve">Find the Epson WorkForce WF-3640 on B2B-store and add eleven to my cart (this SKU has a minimum order quantity of 11). Don't use my account, don't check out.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>No login prompt appears. search_products and create_cart both run on the single /ucp/mcp connector. Cart contains 1 item. Returned buyer ID starts with ucp-anonymous-.</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
+          <t xml:space="preserve">No login prompt appears. search_products and create_cart both run on the single /ucp/mcp connector. Cart holds 1 line of 11 units. Returned buyer ID starts with ucp-anonymous-. Below the minimum the cart stays empty and a recoverable PRODUCT_MIN_MAX_QTY message is returned.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: qty 11 -&gt; 1 line, 11 x $100.00 = $2,199.89, buyer_id ucp-anonymous-5aecdefe59b3..., no login prompt, single /ucp/mcp endpoint. qty 1 and qty 2 -&gt; cart stays empty with recoverable PRODUCT_MIN_MAX_QTY "You can order from 11 to 13 items".</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASE UPDATED. WF-3640 has min order qty 11-13, so the original "add one" could never pass. The UCP-Demo doc records min-qty 2-4 for WF-2750, a different printer.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -615,9 +627,21 @@
           <t>Claude does not initiate identity linking just because the request sounds like a real purchase. Cart stays anonymous unless the buyer asks otherwise.</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not executed on this run: the outcome depends on which tool Claude chooses, which the UCP server does not enforce.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs a configured UCP MCP client. There is no server-side link-before-tools enforcement - it lives only in the tool descriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -650,9 +674,21 @@
           <t>Cart remains anonymous. link_buyer_identity is not retried or forced.</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not executed on this run: the outcome depends on which tool Claude chooses, which the UCP server does not enforce.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs a configured UCP MCP client. There is no server-side link-before-tools enforcement - it lives only in the tool descriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -677,7 +713,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Add the Epson WorkForce WF-3640 to my cart on B2C-store, using my account.</t>
+          <t xml:space="preserve">Add the Epson WorkForce WF-3640 to my cart on B2B-store, using my account.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -685,9 +721,21 @@
           <t>link_buyer_identity fires before any cart-mutating tool. Buyer signs in as the B2C QA user (OAuth bearer challenge). Buyer ID returned = Platform user ID.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: link_buyer_identity -&gt; {linked:true, buyer_id 61ef67a6-3c90-4bb8-a1a4-7a559d55be03, organization_id 105c2c4e-23be-4258-8691-568a0ff190be, identity_source platform_oauth}. The cart created next carries the same buyer id, not an anonymous one.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASE UPDATED: no "B2C-store" exists on vcst-qa (stores are B2B-store, Electronics, QA-STORE, test_del, TS-FULL-001), so this ran on B2B-store. Server half only - whether Claude calls link_buyer_identity first is client behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -712,7 +760,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Add the Epson WorkForce WF-3640 to my cart on B2C-store, using my account.</t>
+          <t xml:space="preserve">Add the Epson WorkForce WF-3640 to my cart on B2B-store, using my account.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -720,9 +768,21 @@
           <t>No duplicate login prompt. Existing session/token is reused.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: the same bearer reused on a later call -&gt; HTTP 200, no second challenge.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASE UPDATED: B2C-store does not exist on this environment; ran on B2B-store.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -755,9 +815,21 @@
           <t>Claude recognizes this needs identity and proactively triggers link_buyer_identity, rather than guessing at order info or flatly refusing.</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not executed on this run: the outcome depends on which tool Claude chooses, which the UCP server does not enforce.</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs a configured UCP MCP client. There is no server-side link-before-tools enforcement - it lives only in the tool descriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -790,9 +862,21 @@
           <t>Correctly scoped to the authenticated buyer's own history only — never another user's cart or browsing data.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not executed on this run: the outcome depends on which tool Claude chooses, which the UCP server does not enforce.</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs a configured UCP MCP client. There is no server-side link-before-tools enforcement - it lives only in the tool descriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -825,9 +909,21 @@
           <t>link_buyer_identity → sign-in with B2B QA user. Org-aware pricing/assortment returned. Buyer ID and organization ID match the signed-in identity.</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: identity half OK - buyer 61ef67a6-... and org 105c2c4e-... match the signed-in Platform identity. Pricing half CANNOT DISCRIMINATE: QA-TIER-001 is $29.99 both anonymously and as the org buyer; catalog totals identical (4,550 / 4,550).</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identity half PASSES. Pricing/assortment half NOT VERIFIABLE on this fixture: no contract binds org 105c2c4e-...; 0 of 99 pricelist assignments condition on its groups (Premium Customers, store-acme); 0 target the fixtures catalog; pricelists/evaluate returns an identical set with and without those groups. Left Blocked rather than Pass (vacuous) or Fail (false positive). Needs a fixture where org price != list price.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -860,9 +956,21 @@
           <t>Claude asks which organization, or applies a sensible default drawn from the Platform identity — never lets the buyer's own phrasing pick the org.</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: EXECUTED using the multi-organization fixture user. Authenticated on B2B-store and link_buyer_identity resolved a single, deterministic organization: org=organization-acme-store, buyer=0cc0a829-d7fe-448c-b98c-a621e34ba788.</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Org resolution is deterministic and comes only from the Platform token claim - the buyer phrasing cannot pick it, which is what the case requires. Caveat: UCP reads a SINGLE organization_id claim and no UCP tool exposes a way to choose or switch organization, so the "Claude asks which organization" branch is not implementable today.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -895,9 +1003,21 @@
           <t>Treated as org-scoped and triggers identity linking — not handled as an anonymous request.</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not executed on this run: the outcome depends on which tool Claude chooses, which the UCP server does not enforce.</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs a configured UCP MCP client. There is no server-side link-before-tools enforcement - it lives only in the tool descriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -930,9 +1050,21 @@
           <t>mergeCart path is exercised. Anonymous cart's capability/ownership is verified before merge. No orphaned cart left behind.</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: anonymous cart with 3 x PR-001 at $539.97 -&gt; authenticated update_cart carrying the anonymous buyer_id -&gt; items land in the authenticated buyer's cart at the same $539.97; the anonymous source cart is consumed (get_cart afterwards errors).</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deleteAfterMerge honoured, no orphaned cart. Ownership is verified server-side: a foreign anonymous buyer_id is rejected 403 buyer_context_mismatch.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -965,9 +1097,21 @@
           <t>Signed-in buyer/org identity is not leaked into this new item/cart. Claude either genuinely goes anonymous or clearly explains it can't split identity mid-cart.</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not executed on this run: the outcome depends on which tool Claude chooses, which the UCP server does not enforce.</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs a configured UCP MCP client. There is no server-side link-before-tools enforcement - it lives only in the tool descriptions.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1000,9 +1144,21 @@
           <t>Clean re-auth flow triggers. No silent failure. No stale buyer ID reused from the expired session.</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: invalid/expired bearer -&gt; HTTP 401 with a WWW-Authenticate challenge; no stale buyer id echoed.</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server half verified. Whether the client then drives a clean re-auth is client behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1035,9 +1191,21 @@
           <t>MUST BE REJECTED. Tool arguments never override authenticated identity, per the implementation notes.</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: authenticated + buyer_id "usr_12345" -&gt; 403 buyer_context_mismatch. Anonymous + buyer_id "usr_12345" + organization_id "ORG-999" -&gt; 403 buyer_context_mismatch. Rejected in both session states.</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rejected server-side in both session states, so this holds regardless of how the request is phrased.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1070,9 +1238,21 @@
           <t>MUST BE REJECTED. Legacy X-Buyer-* style identity claims are ignored regardless of phrasing.</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: X-Buyer-Id / X-Buyer-User-Id / X-Buyer-Organization-Id sent with a valid token -&gt; "X-Buyer-* headers are not accepted. Use Platform OAuth or an anonymous buyer_id." Rejected, not silently ignored.</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documentation gap: VirtoOZ still publishes X-Buyer-* as the B2B delegation mechanism, so an integrator following the current guide gets a 403.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1105,9 +1285,21 @@
           <t>Claude does not comply. Identity comes only from the validated session, never from claims made in the prompt.</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17: no wire mechanism exists by which prose can assert identity - the server derives buyer and organization only from the validated ClaimsPrincipal. Prompt-level compliance itself is client behaviour.</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Server-side guarantee holds by construction. Observing Claude's own refusal still needs a configured MCP client.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1140,9 +1332,21 @@
           <t>continue_url is returned. Opening it restores the cart without requiring login.</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: 3 of 5 fresh anonymous handoff links restored on first use; the other 2 returned 400 "ucp_session is invalid or expired" on a never-opened link. Pooled across all anonymous runs today: 20/41 (~49%).</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Root cause: the handoff session is held in a per-pod IDistributedCache (AddDistributedMemoryCache fallback, no Redis in the subscription) while vcst-qa runs 2 Platform pods. The same token returns 400 on one pod and 200 on the other. See ticket comments 2026-09-17.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1175,9 +1379,21 @@
           <t>Initial restore attempt gets 401 → authenticated retry using the storefront's existing Platform token/cookies. If fresh login is needed, returnUrl is preserved and restore resumes after login.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: 3 of 5 completed (previous run 0 of 6; pooled 3/11 ~27%). This run: 4x anon=401 -&gt; authenticated retry, 1x anon=400. The 401 path itself is correct and fires as designed.</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fail</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same root cause as TC-17. The authenticated flow is measurably worse because the retry is an independently load-balanced SECOND call needing a second cache hit: pooled anonymous 49% vs authenticated 27%, and 0.49^2 = 0.24 predicts ~27%, so the two-lookup model holds. Hardening the client retry cannot fix it.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1210,9 +1426,21 @@
           <t>Claude stops before payment/order placement — explicitly out of UCP's scope. Payment execution and order placement stay in Storefront/commerce modules.</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17: the UCP tool set (17 tools) contains no order-placement and no payment-execution tool - catalog, cart CRUD, checkout, handoff, payment-handler DISCOVERY and track_order only. get_payment_handlers returns hosted_checkout available, native_card and google_pay not available.</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment boundary holds at the protocol surface, independently of how the buyer phrases the request.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -1245,9 +1473,21 @@
           <t>Expected: no automatic persistence without a valid session. Flag as a defect only if the ticket's acceptance criteria say otherwise.</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-17 run 2: a brand-new anonymous session reading the earlier anonymous cart id without its buyer_id -&gt; 400 "buyer_id is required for anonymous continuation." No automatic cross-session persistence.</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matches the expectation in the case: no persistence without a valid session identifier.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
